--- a/docs/202604_勤務表(李到勳) .xlsx
+++ b/docs/202604_勤務表(李到勳) .xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\kintaikanlisystem_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349C2A9D-F840-4278-AB4D-2E3BA526F911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE98822-7E6A-4237-9257-1A33B102F527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>氏　名：</t>
     <rPh sb="0" eb="1">
@@ -223,6 +223,13 @@
     <t>社員マスターテーブル機能、excelインポート機能、
 月別レポートpdf機能</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>リファクタリング</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>午前：マイナンバーカード受け取り、午後：東京ビックサイト</t>
   </si>
 </sst>
 </file>
@@ -545,6 +552,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -573,12 +586,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1074,10 +1081,10 @@
     </row>
     <row r="3" spans="1:10" ht="23.65" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="31">
+      <c r="B3" s="33">
         <v>46113</v>
       </c>
-      <c r="C3" s="31"/>
+      <c r="C3" s="33"/>
       <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
@@ -1137,12 +1144,12 @@
       <c r="B7" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
         <v>15</v>
@@ -1176,22 +1183,22 @@
     </row>
     <row r="10" spans="1:10" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="5"/>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="37"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="13" t="s">
         <v>6</v>
       </c>
@@ -1200,10 +1207,10 @@
     </row>
     <row r="11" spans="1:10" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="5"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
       <c r="F11" s="14" t="s">
         <v>7</v>
       </c>
@@ -1268,7 +1275,7 @@
         <f>SUM(F$12:F13)</f>
         <v>0.625</v>
       </c>
-      <c r="H13" s="38" t="s">
+      <c r="H13" s="27" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="2"/>
@@ -1297,7 +1304,7 @@
         <f>SUM(F$12:F14)</f>
         <v>0.95833333333333326</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="27" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="2"/>
@@ -1320,7 +1327,7 @@
         <f>SUM(F$12:F15)</f>
         <v>0.95833333333333326</v>
       </c>
-      <c r="H15" s="38"/>
+      <c r="H15" s="27"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
@@ -1368,7 +1375,7 @@
         <f>SUM(F$12:F17)</f>
         <v>1.2916666666666665</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="27" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="2"/>
@@ -1426,7 +1433,7 @@
         <f>SUM(F$12:F19)</f>
         <v>1.958333333333333</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="28" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="2"/>
@@ -1438,18 +1445,26 @@
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C20" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="E20" s="11">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F20" s="19">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="G20" s="19">
         <f>SUM(F$12:F20)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H20" s="38"/>
+        <v>2.2916666666666665</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>24</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
@@ -1459,18 +1474,26 @@
         <f t="shared" si="2"/>
         <v>46122</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C21" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="E21" s="11">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F21" s="19">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="G21" s="19">
         <f>SUM(F$12:F21)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H21" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
@@ -1489,9 +1512,9 @@
       </c>
       <c r="G22" s="19">
         <f>SUM(F$12:F22)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H22" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H22" s="27"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
@@ -1510,9 +1533,9 @@
       </c>
       <c r="G23" s="19">
         <f>SUM(F$12:F23)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H23" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H23" s="27"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
@@ -1531,9 +1554,9 @@
       </c>
       <c r="G24" s="19">
         <f>SUM(F$12:F24)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H24" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H24" s="27"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
@@ -1552,7 +1575,7 @@
       </c>
       <c r="G25" s="19">
         <f>SUM(F$12:F25)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="2"/>
@@ -1573,7 +1596,7 @@
       </c>
       <c r="G26" s="19">
         <f>SUM(F$12:F26)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="2"/>
@@ -1594,9 +1617,9 @@
       </c>
       <c r="G27" s="19">
         <f>SUM(F$12:F27)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H27" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H27" s="27"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
@@ -1615,9 +1638,9 @@
       </c>
       <c r="G28" s="19">
         <f>SUM(F$12:F28)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H28" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H28" s="27"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
@@ -1636,9 +1659,9 @@
       </c>
       <c r="G29" s="19">
         <f>SUM(F$12:F29)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H29" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H29" s="27"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
@@ -1657,9 +1680,9 @@
       </c>
       <c r="G30" s="19">
         <f>SUM(F$12:F30)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H30" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H30" s="27"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
@@ -1678,7 +1701,7 @@
       </c>
       <c r="G31" s="19">
         <f>SUM(F$12:F31)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="2"/>
@@ -1699,7 +1722,7 @@
       </c>
       <c r="G32" s="19">
         <f>SUM(F$12:F32)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H32" s="26"/>
       <c r="I32" s="2"/>
@@ -1720,7 +1743,7 @@
       </c>
       <c r="G33" s="19">
         <f>SUM(F$12:F33)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="2"/>
@@ -1741,9 +1764,9 @@
       </c>
       <c r="G34" s="19">
         <f>SUM(F$12:F34)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H34" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H34" s="27"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
@@ -1762,7 +1785,7 @@
       </c>
       <c r="G35" s="19">
         <f>SUM(F$12:F35)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="2"/>
@@ -1783,9 +1806,9 @@
       </c>
       <c r="G36" s="19">
         <f>SUM(F$12:F36)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H36" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H36" s="27"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
@@ -1804,9 +1827,9 @@
       </c>
       <c r="G37" s="19">
         <f>SUM(F$12:F37)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H37" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H37" s="27"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
@@ -1825,9 +1848,9 @@
       </c>
       <c r="G38" s="19">
         <f>SUM(F$12:F38)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H38" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H38" s="27"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
     </row>
@@ -1846,9 +1869,9 @@
       </c>
       <c r="G39" s="19">
         <f>SUM(F$12:F39)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H39" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H39" s="27"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
@@ -1867,9 +1890,9 @@
       </c>
       <c r="G40" s="19">
         <f>SUM(F$12:F40)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H40" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H40" s="27"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
@@ -1888,9 +1911,9 @@
       </c>
       <c r="G41" s="19">
         <f>SUM(F$12:F41)</f>
-        <v>1.958333333333333</v>
-      </c>
-      <c r="H41" s="38"/>
+        <v>2.625</v>
+      </c>
+      <c r="H41" s="27"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
@@ -1909,7 +1932,7 @@
       </c>
       <c r="G42" s="19">
         <f>SUM(F$12:F42)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="2"/>
@@ -1917,16 +1940,16 @@
     </row>
     <row r="43" spans="1:12" ht="18.649999999999999" customHeight="1" thickTop="1">
       <c r="A43" s="2"/>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="32"/>
       <c r="G43" s="21">
         <f>SUM(F$12:F43)</f>
-        <v>1.958333333333333</v>
+        <v>2.625</v>
       </c>
       <c r="H43" s="16"/>
       <c r="I43" s="2"/>

--- a/docs/202604_勤務表(李到勳) .xlsx
+++ b/docs/202604_勤務表(李到勳) .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\kintaikanlisystem_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE98822-7E6A-4237-9257-1A33B102F527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40C36D0-4A3F-4D3F-8B3B-682984E90209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2390" windowWidth="16920" windowHeight="9560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年4月" sheetId="25" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>氏　名：</t>
     <rPh sb="0" eb="1">
@@ -230,6 +230,10 @@
   </si>
   <si>
     <t>午前：マイナンバーカード受け取り、午後：東京ビックサイト</t>
+  </si>
+  <si>
+    <t>CSV読み込み機能、月ごとに入力機能</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1545,18 +1549,26 @@
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C24" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="11">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F24" s="19">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="G24" s="19">
         <f>SUM(F$12:F24)</f>
-        <v>2.625</v>
-      </c>
-      <c r="H24" s="27"/>
+        <v>2.9583333333333335</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>26</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
@@ -1575,7 +1587,7 @@
       </c>
       <c r="G25" s="19">
         <f>SUM(F$12:F25)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="2"/>
@@ -1596,7 +1608,7 @@
       </c>
       <c r="G26" s="19">
         <f>SUM(F$12:F26)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="2"/>
@@ -1617,7 +1629,7 @@
       </c>
       <c r="G27" s="19">
         <f>SUM(F$12:F27)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H27" s="27"/>
       <c r="I27" s="2"/>
@@ -1638,7 +1650,7 @@
       </c>
       <c r="G28" s="19">
         <f>SUM(F$12:F28)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H28" s="27"/>
       <c r="I28" s="2"/>
@@ -1659,7 +1671,7 @@
       </c>
       <c r="G29" s="19">
         <f>SUM(F$12:F29)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H29" s="27"/>
       <c r="I29" s="2"/>
@@ -1680,7 +1692,7 @@
       </c>
       <c r="G30" s="19">
         <f>SUM(F$12:F30)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H30" s="27"/>
       <c r="I30" s="2"/>
@@ -1701,7 +1713,7 @@
       </c>
       <c r="G31" s="19">
         <f>SUM(F$12:F31)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="2"/>
@@ -1722,7 +1734,7 @@
       </c>
       <c r="G32" s="19">
         <f>SUM(F$12:F32)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H32" s="26"/>
       <c r="I32" s="2"/>
@@ -1743,7 +1755,7 @@
       </c>
       <c r="G33" s="19">
         <f>SUM(F$12:F33)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="2"/>
@@ -1764,7 +1776,7 @@
       </c>
       <c r="G34" s="19">
         <f>SUM(F$12:F34)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H34" s="27"/>
       <c r="I34" s="2"/>
@@ -1785,7 +1797,7 @@
       </c>
       <c r="G35" s="19">
         <f>SUM(F$12:F35)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="2"/>
@@ -1806,7 +1818,7 @@
       </c>
       <c r="G36" s="19">
         <f>SUM(F$12:F36)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="2"/>
@@ -1827,7 +1839,7 @@
       </c>
       <c r="G37" s="19">
         <f>SUM(F$12:F37)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H37" s="27"/>
       <c r="I37" s="2"/>
@@ -1848,7 +1860,7 @@
       </c>
       <c r="G38" s="19">
         <f>SUM(F$12:F38)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H38" s="27"/>
       <c r="I38" s="2"/>
@@ -1869,7 +1881,7 @@
       </c>
       <c r="G39" s="19">
         <f>SUM(F$12:F39)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H39" s="27"/>
       <c r="I39" s="2"/>
@@ -1890,7 +1902,7 @@
       </c>
       <c r="G40" s="19">
         <f>SUM(F$12:F40)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="2"/>
@@ -1911,7 +1923,7 @@
       </c>
       <c r="G41" s="19">
         <f>SUM(F$12:F41)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H41" s="27"/>
       <c r="I41" s="2"/>
@@ -1932,7 +1944,7 @@
       </c>
       <c r="G42" s="19">
         <f>SUM(F$12:F42)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="2"/>
@@ -1949,7 +1961,7 @@
       <c r="F43" s="32"/>
       <c r="G43" s="21">
         <f>SUM(F$12:F43)</f>
-        <v>2.625</v>
+        <v>2.9583333333333335</v>
       </c>
       <c r="H43" s="16"/>
       <c r="I43" s="2"/>
